--- a/redbookaccontidandresult.xlsx
+++ b/redbookaccontidandresult.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11013"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yc/Desktop/program/python/MediaCrawler/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2610A2-EBCF-F34A-9DA9-BF411000481D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14100" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="14100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小红书账号" sheetId="2" r:id="rId1"/>
@@ -15,12 +21,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,18 +43,6 @@
     <t>Spark Math线上教育</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="9.75"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://www.xiaohongshu.com/user/profile/62b16791000000001501b2ca?xsec_token=ABcuAQdC6Rl_JEnJBu4zyKSt2rWnqOGZziFsERDZ75E34%3D&amp;xsec_source=pc_search</t>
-    </r>
-  </si>
-  <si>
     <t>Spark Math线上课程</t>
   </si>
   <si>
@@ -63,7 +52,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/61b2fc7e000000001000f059?xsec_token=ABQbA2jfbtHRkm9ZR9qrHBX82eEF9XrpDAaSfKyQ7GJwE%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -78,7 +67,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/64740b96000000000f006adf?xsec_token=ABCs_kSHJnIumJb8ljNZdvgTLxYBd3dJJEmKunc4S3avI%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -93,7 +82,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/5ff43d2b0000000001001995?xsec_token=AByizwCWrT0j9ZFadOJIHNUN2WGVEqO2X9fzCpLg6qtYw%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -108,7 +97,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/6504601f0000000017021a03?xsec_token=ABC4Vv622sP46BO2rIcQnhgqe3qa69-dXTyi34EGyy_7o%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -123,7 +112,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/66c8466d000000001d02328b?xsec_token=AB3fFtBtFfy31iC5R2VyPBnmZxZZNhwvy0iRS4APcvvA0%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -138,7 +127,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/61b2c64e0000000010007500?xsec_token=ABQbA2jfbtHRkm9ZR9qrHBXz7vppg8mr_xgD-HMLJluBY%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -153,7 +142,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/66c854d2000000001d022cac?xsec_token=AB3fFtBtFfy31iC5R2VyPBngZ7jc4MKnWSvVJCQAun8r8%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -168,7 +157,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/66dea45e000000000d026777?xsec_token=AB9bVijV-V2KufmqZfN14BbvrWmHmgnTcoD0LXF6mlLAc%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -183,7 +172,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/642a3b7f000000001102347e?xsec_token=ABQYAZcJFqLSVNO7sPgqg1MAjLCcqtCHFmHfhU7fg5mro%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -198,7 +187,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/642ba9780000000012011a80?xsec_token=ABdM_4WwX6A2aWcBGvarVBatEbJ_qWS2j_gQnWFhqMy44%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -213,7 +202,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/649e933900000000140344d9?xsec_token=ABE7IMTH_dsTUPE7nS4I0X9V45tyBMDjl5bns295kNBXw%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -228,7 +217,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/649a8fdf000000001f0060ff?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpz7Tqc1QpD29k3gjr_-ZfA%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -243,7 +232,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/649a70220000000010036bfc?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpibKag82SYNPUD6MYF5K_E%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -258,7 +247,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/6735499c000000001600b1b9?xsec_token=ABpQZMVSjkTk5dn-0UHKi84HnZZCUk8uvGqqUpRPjDasw%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -273,7 +262,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/636b58ff000000001f01a10d?xsec_token=ABfdrt_O7s1QqiR7bsfFJo8JMGhL40VY-MlyF3MKNrIck%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -288,7 +277,7 @@
         <sz val="9.75"/>
         <color theme="10"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.xiaohongshu.com/user/profile/649a8e5f000000001001c410?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnt-yYvcj9ZQWyCHgZ4O4Lto%3D&amp;xsec_source=pc_search</t>
     </r>
@@ -335,18 +324,16 @@
   <si>
     <t>视频脚本内容（文字形式）</t>
   </si>
+  <si>
+    <t>https://www.xiaohongshu.com/user/profile/62b16791000000001501b2ca?xsec_token=ABcuAQdC6Rl_JEnJBu4zyKSt2rWnqOGZziFsERDZ75E34%3D&amp;xsec_source=pc_search</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -366,157 +353,14 @@
       <sz val="9.75"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -524,204 +368,31 @@
       <sz val="9.75"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -729,253 +400,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -988,62 +420,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1301,18 +693,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="25.19921875" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="137" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1327,271 +721,271 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="15">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2">
         <v>4155118020</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="14">
+      <c r="A3" s="2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="B3" s="2">
         <v>6952581888</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="14">
+      <c r="A4" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="B4" s="2">
         <v>9745003706</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="14">
+      <c r="A5" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>1111039964</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="14">
+      <c r="A6" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="B6" s="2">
         <v>5838470932</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="14">
+      <c r="A7" s="2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="B7" s="2">
         <v>95420183564</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="14">
+      <c r="A8" s="2" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>2114808802</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="14">
+      <c r="A9" s="2" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="B9" s="2">
         <v>95420616195</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="14">
+      <c r="A10" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="B10" s="2">
         <v>94183399129</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="14">
+      <c r="A11" s="2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="B11" s="2">
         <v>7470831848</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="14">
+      <c r="A12" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="B12" s="2">
         <v>6148171953</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="14">
+      <c r="A13" s="2" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="B13" s="2">
         <v>3154036797</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="14">
+      <c r="A14" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="B14" s="2">
         <v>4355493542</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="14">
+      <c r="A15" s="2" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="B15" s="2">
         <v>6861340353</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="14">
+      <c r="A16" s="2" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="B16" s="2">
         <v>95659673000</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14">
+      <c r="A17" s="2" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="B17" s="2">
         <v>5332041829</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14">
+      <c r="A18" s="2" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="B18" s="2">
         <v>8996268697</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14">
+      <c r="A19" s="2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="B19" s="2">
         <v>94181569559</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://www.xiaohongshu.com/user/profile/62b16791000000001501b2ca?xsec_token=ABcuAQdC6Rl_JEnJBu4zyKSt2rWnqOGZziFsERDZ75E34%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C10" r:id="rId2" display="https://www.xiaohongshu.com/user/profile/66dea45e000000000d026777?xsec_token=AB9bVijV-V2KufmqZfN14BbvrWmHmgnTcoD0LXF6mlLAc%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C9" r:id="rId3" display="https://www.xiaohongshu.com/user/profile/66c854d2000000001d022cac?xsec_token=AB3fFtBtFfy31iC5R2VyPBngZ7jc4MKnWSvVJCQAun8r8%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C7" r:id="rId4" display="https://www.xiaohongshu.com/user/profile/66c8466d000000001d02328b?xsec_token=AB3fFtBtFfy31iC5R2VyPBnmZxZZNhwvy0iRS4APcvvA0%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C15" r:id="rId5" display="https://www.xiaohongshu.com/user/profile/649a70220000000010036bfc?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpibKag82SYNPUD6MYF5K_E%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C19" r:id="rId6" display="https://www.xiaohongshu.com/user/profile/669f40a3000000001e00b482?xsec_token=AB0Dg1lCKW-goumU5eGwNUGVqVJVzJ3-N6CyRW7KEwofo%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C16" r:id="rId7" display="https://www.xiaohongshu.com/user/profile/6735499c000000001600b1b9?xsec_token=ABpQZMVSjkTk5dn-0UHKi84HnZZCUk8uvGqqUpRPjDasw%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C3" r:id="rId8" display="https://www.xiaohongshu.com/user/profile/61b2fc7e000000001000f059?xsec_token=ABQbA2jfbtHRkm9ZR9qrHBX82eEF9XrpDAaSfKyQ7GJwE%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C13" r:id="rId9" display="https://www.xiaohongshu.com/user/profile/649e933900000000140344d9?xsec_token=ABE7IMTH_dsTUPE7nS4I0X9V45tyBMDjl5bns295kNBXw%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C14" r:id="rId10" display="https://www.xiaohongshu.com/user/profile/649a8fdf000000001f0060ff?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpz7Tqc1QpD29k3gjr_-ZfA%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C11" r:id="rId11" display="https://www.xiaohongshu.com/user/profile/642a3b7f000000001102347e?xsec_token=ABQYAZcJFqLSVNO7sPgqg1MAjLCcqtCHFmHfhU7fg5mro%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C12" r:id="rId12" display="https://www.xiaohongshu.com/user/profile/642ba9780000000012011a80?xsec_token=ABdM_4WwX6A2aWcBGvarVBatEbJ_qWS2j_gQnWFhqMy44%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C8" r:id="rId13" display="https://www.xiaohongshu.com/user/profile/61b2c64e0000000010007500?xsec_token=ABQbA2jfbtHRkm9ZR9qrHBXz7vppg8mr_xgD-HMLJluBY%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C4" r:id="rId14" display="https://www.xiaohongshu.com/user/profile/64740b96000000000f006adf?xsec_token=ABCs_kSHJnIumJb8ljNZdvgTLxYBd3dJJEmKunc4S3avI%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C6" r:id="rId15" display="https://www.xiaohongshu.com/user/profile/6504601f0000000017021a03?xsec_token=ABC4Vv622sP46BO2rIcQnhgqe3qa69-dXTyi34EGyy_7o%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C5" r:id="rId16" display="https://www.xiaohongshu.com/user/profile/5ff43d2b0000000001001995?xsec_token=AByizwCWrT0j9ZFadOJIHNUN2WGVEqO2X9fzCpLg6qtYw%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C18" r:id="rId17" display="https://www.xiaohongshu.com/user/profile/649a8e5f000000001001c410?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnt-yYvcj9ZQWyCHgZ4O4Lto%3D&amp;xsec_source=pc_search"/>
-    <hyperlink ref="C17" r:id="rId18" display="https://www.xiaohongshu.com/user/profile/636b58ff000000001f01a10d?xsec_token=ABfdrt_O7s1QqiR7bsfFJo8JMGhL40VY-MlyF3MKNrIck%3D&amp;xsec_source=pc_search"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C19" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C16" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C3" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C4" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C6" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C5" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <picture r:id="rId19"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:W200"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="7" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" ht="14">
       <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1608,10 +1002,10 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" ht="14">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1619,10 +1013,10 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -6590,8 +5984,8 @@
       <c r="W200" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <picture r:id="rId1"/>
 </worksheet>
 </file>
--- a/redbookaccontidandresult.xlsx
+++ b/redbookaccontidandresult.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,185 +606,168 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>学而思网校官方账号</t>
+          <t>平行线根源在线数学</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>94183399129</t>
+          <t>7470831848</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/66dea45e000000000d026777?xsec_token=AB9bVijV-V2KufmqZfN14BbvrWmHmgnTcoD0LXF6mlLAc%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/642a3b7f000000001102347e?xsec_token=ABQYAZcJFqLSVNO7sPgqg1MAjLCcqtCHFmHfhU7fg5mro%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>平行线根源在线数学</t>
+          <t>平行线名师大课堂</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7470831848</t>
+          <t>6148171953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/642a3b7f000000001102347e?xsec_token=ABQYAZcJFqLSVNO7sPgqg1MAjLCcqtCHFmHfhU7fg5mro%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/642ba9780000000012011a80?xsec_token=ABdM_4WwX6A2aWcBGvarVBatEbJ_qWS2j_gQnWFhqMy44%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>平行线名师大课堂</t>
+          <t>掌门1对1特训营</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6148171953</t>
+          <t>3154036797</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/642ba9780000000012011a80?xsec_token=ABdM_4WwX6A2aWcBGvarVBatEbJ_qWS2j_gQnWFhqMy44%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/649e933900000000140344d9?xsec_token=ABE7IMTH_dsTUPE7nS4I0X9V45tyBMDjl5bns295kNBXw%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>掌门1对1特训营</t>
+          <t>掌门1对1素养</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3154036797</t>
+          <t>4355493542</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/649e933900000000140344d9?xsec_token=ABE7IMTH_dsTUPE7nS4I0X9V45tyBMDjl5bns295kNBXw%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/649a8fdf000000001f0060ff?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpz7Tqc1QpD29k3gjr_-ZfA%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>掌门1对1素养</t>
+          <t>掌门1对1学习中心</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4355493542</t>
+          <t>6861340353</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/649a8fdf000000001f0060ff?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpz7Tqc1QpD29k3gjr_-ZfA%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/649a70220000000010036bfc?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpibKag82SYNPUD6MYF5K_E%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>掌门1对1学习中心</t>
+          <t>掌门1对1学习规划</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6861340353</t>
+          <t>95659673000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/649a70220000000010036bfc?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnpibKag82SYNPUD6MYF5K_E%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/6735499c000000001600b1b9?xsec_token=ABpQZMVSjkTk5dn-0UHKi84HnZZCUk8uvGqqUpRPjDasw%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>掌门1对1学习规划</t>
+          <t>掌门1对1规划</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>95659673000</t>
+          <t>5332041829</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/6735499c000000001600b1b9?xsec_token=ABpQZMVSjkTk5dn-0UHKi84HnZZCUk8uvGqqUpRPjDasw%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/636b58ff000000001f01a10d?xsec_token=ABfdrt_O7s1QqiR7bsfFJo8JMGhL40VY-MlyF3MKNrIck%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>掌门1对1规划</t>
+          <t>掌门1对1知识分享</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5332041829</t>
+          <t>8996268697</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/636b58ff000000001f01a10d?xsec_token=ABfdrt_O7s1QqiR7bsfFJo8JMGhL40VY-MlyF3MKNrIck%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/649a8e5f000000001001c410?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnt-yYvcj9ZQWyCHgZ4O4Lto%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>掌门1对1知识分享</t>
+          <t>掌门1对1逆袭</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8996268697</t>
+          <t>94181569559</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/user/profile/649a8e5f000000001001c410?xsec_token=AB_qIAhR5BD9jBu8CMyQrnnt-yYvcj9ZQWyCHgZ4O4Lto%3D&amp;xsec_source=pc_search</t>
+          <t>https://www.xiaohongshu.com/user/profile/669f40a3000000001e00b482?xsec_token=AB0Dg1lCKW-goumU5eGwNUGVqVJVzJ3-N6CyRW7KEwofo%3D&amp;xsec_source=pc_search</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>掌门1对1逆袭</t>
+          <t>高途学习中心</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>94181569559</t>
+          <t>4986011641</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/user/profile/669f40a3000000001e00b482?xsec_token=AB0Dg1lCKW-goumU5eGwNUGVqVJVzJ3-N6CyRW7KEwofo%3D&amp;xsec_source=pc_search</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>高途学习中心</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>4986011641</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>https://www.xiaohongshu.com/user/profile/61547bfe0000000002018998?m_source=pwa&amp;channel_type=web_search_result_notes&amp;parent_page_channel_type=web_profile_board&amp;xsec_token=ABGDXXr3kdW1qv3Vo_Wlyu_8p_ZKLkC4qiTL5yVwnF5Oc=&amp;xsec_source=pc_search</t>
         </is>
